--- a/강의예제/8장_실무에서_필요한_데이터_시각화/8장_종합문제.xlsx
+++ b/강의예제/8장_실무에서_필요한_데이터_시각화/8장_종합문제.xlsx
@@ -652,8 +652,8 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>지금 이렇게 그려져 있습니다 —
-세로 축이 600 부터 시작합니다.
-서울 막대가 대구 막대의 열 배쯤 되어 보입니다.</t>
+세로 축이 50 부터 시작합니다.
+서울 막대가 대구 막대의 열네 배쯤 되어 보입니다.</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>막대는 길이가 값입니다. 600 부터 시작하면 698 과 301 의 차이가 실제보다 커 보입니다.</t>
+          <t>막대는 길이가 값입니다. 50 부터 시작하면 서울과 대구가 열네 배로 보입니다 — 실제는 7.3배.</t>
         </is>
       </c>
     </row>

--- a/강의예제/8장_실무에서_필요한_데이터_시각화/8장_종합문제.xlsx
+++ b/강의예제/8장_실무에서_필요한_데이터_시각화/8장_종합문제.xlsx
@@ -232,6 +232,534 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>지역별 합격자 수</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'문제'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$5:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$C$5:$C$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="50"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>지역별 합격자 수</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'문제'!C22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$23:$B$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$C$23:$C$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>영업1팀 분기 실적</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'문제'!C40</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$41:$B$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$C$41:$C$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>제품별 점유율</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'문제'!C58</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$59:$B$67</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$C$59:$C$67</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>GDP와 성장률</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'문제'!C76</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$77:$B$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$C$77:$C$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'문제'!D76</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'문제'!$B$77:$B$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'문제'!$D$77:$D$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,7 +1079,8 @@
   보고서에 들어갈 차트 **네 개**를 받았습니다.
   **넷 다 어딘가 거짓말을 하고 있습니다.**
   [문제] 시트에 각 차트의 자료와 **지금 어떻게 그려져 있는지**가 적혀 있습니다.
-  직접 차트를 그려 보고, **무엇이 잘못됐는지 찾아 고치세요.**
+  차트는 [문제] 시트 **오른쪽(H열)에 이미 그려져** 있습니다.
+  **무엇이 잘못됐는지 찾아 고치세요.** 5번은 곁들여 보는 것입니다.
 ■ 여섯 단계 — 순서대로
   ① 1번 — 막대   세로 축 최소값을 확인합니다                     (8-02)
   ② 2번 — 가로막대 항목 순서를 확인합니다                        (8-02)
@@ -613,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F43"/>
+  <dimension ref="B1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -627,7 +1156,7 @@
     <row r="1">
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>자료는 손대지 마세요. 차트를 그려 보고 무엇이 잘못됐는지 찾는 문제입니다.</t>
+          <t>자료는 손대지 마세요. 오른쪽(H열)에 그려진 차트 다섯 개를 보고 무엇이 잘못됐는지 찾는 문제입니다.</t>
         </is>
       </c>
     </row>
@@ -707,25 +1236,25 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2번 — 같은 자료 (가로 막대)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>시도</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>인원</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>지금 이렇게 그려져 있습니다 —
 1등 서울이 차트 맨 아래에 있습니다.
@@ -733,75 +1262,75 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C23" s="7" t="n">
         <v>698</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>경기도</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C24" s="7" t="n">
         <v>301</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>부산광역시</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C25" s="7" t="n">
         <v>142</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>인천광역시</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C26" s="7" t="n">
         <v>118</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>대구광역시</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C27" s="7" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>3번 — 영업1팀 분기 실적 (꺾은선)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>분기</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>실적(억)</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>지금 이렇게 그려져 있습니다 —
 네 점이 같은 실선으로 이어져 있습니다.
@@ -809,65 +1338,65 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>1분기</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C41" s="7" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>2분기</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C42" s="7" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>3분기</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C43" s="7" t="n">
         <v>118</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>4분기(예상)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C44" s="7" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>4번 — 제품별 점유율 (원형)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>제품</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>점유율(%)</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>지금 이렇게 그려져 있습니다 —
 조각이 아홉 개입니다. 범례가 오른쪽에 있고
@@ -875,120 +1404,120 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>A제품</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C59" s="7" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="7" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>B제품</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C60" s="7" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>C제품</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C61" s="7" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>D제품</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C62" s="7" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="7" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>E제품</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C63" s="7" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="7" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>F제품</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C64" s="7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>G제품</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C65" s="7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="7" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>H제품</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C66" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="7" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>I제품</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C67" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>5번 — 곁들여 — GDP와 성장률 (혼합)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>년도</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>GDP(십억)</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>성장률</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>지금 이렇게 그려져 있습니다 —
 둘 다 막대로 그려져 있습니다.
@@ -996,52 +1525,53 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="7" t="n">
+    <row r="77">
+      <c r="B77" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C77" s="8" t="n">
         <v>2236330</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D77" s="9" t="n">
         <v>0.0136</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="7" t="n">
+    <row r="78">
+      <c r="B78" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C78" s="8" t="n">
         <v>2305271</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D78" s="9" t="n">
         <v>0.0208</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="7" t="n">
+    <row r="79">
+      <c r="B79" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C79" s="8" t="n">
         <v>2401800</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D79" s="9" t="n">
         <v>0.0419</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="7" t="n">
+    <row r="80">
+      <c r="B80" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C80" s="8" t="n">
         <v>2468500</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D80" s="9" t="n">
         <v>0.0278</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
